--- a/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:13:31+00:00</t>
+    <t>2026-09-14T10:10:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T10:10:05+00:00</t>
+    <t>2026-09-14T15:22:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T15:22:50+00:00</t>
+    <t>2026-09-15T13:50:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T13:50:59+00:00</t>
+    <t>2026-09-16T10:28:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T10:28:49+00:00</t>
+    <t>2026-09-17T09:27:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T09:27:26+00:00</t>
+    <t>2026-09-17T15:49:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T15:49:54+00:00</t>
+    <t>2026-09-22T07:57:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
